--- a/01_Thermal/B_results/single_var_analysis.xlsx
+++ b/01_Thermal/B_results/single_var_analysis.xlsx
@@ -493,25 +493,25 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>41.07993091775862</v>
+        <v>32.19026328703165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5134815249767212</v>
+        <v>0.501122966470203</v>
       </c>
       <c r="F2" t="n">
-        <v>3164.921821633475</v>
+        <v>3014.407460168541</v>
       </c>
       <c r="G2" t="n">
         <v>12003.65050354092</v>
       </c>
       <c r="H2" t="n">
-        <v>9.818716009997178</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="3">
@@ -527,25 +527,25 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>16.71610475990278</v>
+        <v>16.69625739866476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1942557352263556</v>
+        <v>0.1933160657503327</v>
       </c>
       <c r="F3" t="n">
-        <v>369.9263558153873</v>
+        <v>366.3561367470614</v>
       </c>
       <c r="G3" t="n">
         <v>9803.193489796937</v>
       </c>
       <c r="H3" t="n">
-        <v>6.770606011794624</v>
+        <v>6.673280221219097</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4887648872788611</v>
+        <v>0.496794616738258</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002531838719378787</v>
+        <v>0.001727985030488321</v>
       </c>
     </row>
     <row r="4">
@@ -561,25 +561,25 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>23.22593164781632</v>
+        <v>21.91716162517541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4002375230363378</v>
+        <v>0.4147267082515927</v>
       </c>
       <c r="F4" t="n">
-        <v>1456.282973243095</v>
+        <v>1563.63065736158</v>
       </c>
       <c r="G4" t="n">
         <v>9090.968804657296</v>
       </c>
       <c r="H4" t="n">
-        <v>5.545970949951866</v>
+        <v>3.291672626834771</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6090783651875445</v>
+        <v>0.7031244562920843</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001164258275031974</v>
+        <v>-0.00182925596811175</v>
       </c>
     </row>
     <row r="5">
@@ -595,25 +595,25 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>16.23883091756838</v>
+        <v>16.18934620144853</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09128529284178849</v>
+        <v>0.09191999901387572</v>
       </c>
       <c r="F5" t="n">
-        <v>596.9831168335306</v>
+        <v>605.3136185552994</v>
       </c>
       <c r="G5" t="n">
         <v>71640.79933933764</v>
       </c>
       <c r="H5" t="n">
-        <v>3.970100616203556</v>
+        <v>3.914862849292072</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6298678560555186</v>
+        <v>0.6433688944307844</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01142640831556188</v>
+        <v>0.009147623214956957</v>
       </c>
     </row>
     <row r="6">
@@ -629,25 +629,25 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>14.02062458033317</v>
+        <v>14.08364846755489</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1466549582403301</v>
+        <v>0.148641043324522</v>
       </c>
       <c r="F6" t="n">
-        <v>345.1265431190374</v>
+        <v>354.5376407012808</v>
       </c>
       <c r="G6" t="n">
         <v>16046.66774128612</v>
       </c>
       <c r="H6" t="n">
-        <v>2.957780394786506</v>
+        <v>3.029721252549284</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6999404560883336</v>
+        <v>0.7027402961340202</v>
       </c>
       <c r="J6" t="n">
-        <v>9.537204570494757e-06</v>
+        <v>-0.0009037041805251279</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>15.91050539726832</v>
+        <v>15.23810056411856</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2108726295632613</v>
+        <v>0.2245796228157905</v>
       </c>
       <c r="F7" t="n">
-        <v>240.3036319745142</v>
+        <v>272.5590479998502</v>
       </c>
       <c r="G7" t="n">
         <v>5404.056829595333</v>
       </c>
       <c r="H7" t="n">
-        <v>3.185712397796389</v>
+        <v>3.110588816707562</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6999562287719225</v>
+        <v>0.744074370343986</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02006838017244906</v>
+        <v>-0.01137067090462262</v>
       </c>
     </row>
     <row r="8">
@@ -697,25 +697,25 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>10.68377162924604</v>
+        <v>11.63960085955972</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08700157605068753</v>
+        <v>0.09124833073880327</v>
       </c>
       <c r="F8" t="n">
-        <v>147.7893463042574</v>
+        <v>162.5693783081241</v>
       </c>
       <c r="G8" t="n">
         <v>19524.90314262347</v>
       </c>
       <c r="H8" t="n">
-        <v>2.582349146612595</v>
+        <v>2.4535639299596</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7728403324973639</v>
+        <v>0.8300884365084038</v>
       </c>
       <c r="J8" t="n">
-        <v>8.906684255805767e-05</v>
+        <v>-0.006633976675569533</v>
       </c>
     </row>
     <row r="9">
@@ -729,13 +729,13 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>137.8756998498936</v>
+        <v>127.9543784035535</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2098731418721428</v>
+        <v>0.2101724019534848</v>
       </c>
       <c r="F9" t="n">
-        <v>6321.333788923296</v>
+        <v>6339.373939841737</v>
       </c>
       <c r="G9" t="n">
         <v>143514.2398508377</v>
